--- a/data/trans_dic/P56$auxiliar-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P56$auxiliar-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>13,22%</t>
         </is>
       </c>
     </row>
@@ -722,57 +722,57 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,3</t>
+          <t>0,0; 21,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,96</t>
+          <t>0,0; 21,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,24; 18,72</t>
+          <t>3,21; 17,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,95</t>
+          <t>0,0; 21,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,2; 16,81</t>
+          <t>2,2; 18,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,53</t>
+          <t>0,0; 16,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,99; 22,56</t>
+          <t>9,31; 23,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,4</t>
+          <t>0,0; 12,35</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,59; 14,33</t>
+          <t>1,53; 15,02</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,62</t>
+          <t>0,0; 15,0</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,97; 18,83</t>
+          <t>8,47; 18,92</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,57%</t>
         </is>
       </c>
     </row>
@@ -862,57 +862,57 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,64; 25,02</t>
+          <t>6,09; 26,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 14,65</t>
+          <t>1,63; 15,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19,02; 36,78</t>
+          <t>19,55; 36,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,06; 16,3</t>
+          <t>3,05; 16,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,14; 30,69</t>
+          <t>16,99; 31,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,01; 13,58</t>
+          <t>3,71; 14,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>26,81; 35,95</t>
+          <t>26,26; 35,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,07; 11,64</t>
+          <t>1,98; 10,66</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15,91; 27,21</t>
+          <t>15,73; 26,6</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,24; 12,73</t>
+          <t>4,12; 12,36</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>25,83; 34,09</t>
+          <t>25,27; 33,55</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,72%</t>
         </is>
       </c>
     </row>
@@ -1002,57 +1002,57 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,47; 20,6</t>
+          <t>4,85; 20,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,24; 13,04</t>
+          <t>2,18; 13,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,63; 29,28</t>
+          <t>15,47; 28,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,34; 13,1</t>
+          <t>2,41; 13,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,2; 26,26</t>
+          <t>14,51; 25,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,08; 11,8</t>
+          <t>3,06; 12,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23,68; 31,58</t>
+          <t>24,08; 31,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,64; 10,23</t>
+          <t>1,62; 9,73</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13,26; 21,85</t>
+          <t>13,3; 23,07</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,68; 10,65</t>
+          <t>3,67; 10,29</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22,57; 29,6</t>
+          <t>22,61; 29,23</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2699</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7897</t>
+          <t>9257</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10541</t>
+          <t>11956</t>
         </is>
       </c>
     </row>
@@ -1368,57 +1368,57 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5851</t>
+          <t>0; 4658</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5056</t>
+          <t>0; 4466</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>961; 5551</t>
+          <t>995; 5570</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4624</t>
+          <t>0; 4742</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>927; 7083</t>
+          <t>927; 7802</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 8042</t>
+          <t>0; 6616</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4762; 11955</t>
+          <t>5537; 14106</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3981</t>
+          <t>0; 4314</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1013; 9111</t>
+          <t>975; 9550</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 8483</t>
+          <t>0; 9340</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6584; 15562</t>
+          <t>7664; 17116</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19528</t>
+          <t>20781</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>61078</t>
+          <t>66038</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>80606</t>
+          <t>86819</t>
         </is>
       </c>
     </row>
@@ -1576,57 +1576,57 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3216; 14281</t>
+          <t>3478; 15023</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>812; 7473</t>
+          <t>829; 7685</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13775; 26632</t>
+          <t>15173; 28000</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2188; 11653</t>
+          <t>2182; 11993</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27955; 50058</t>
+          <t>27716; 50638</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3934; 17735</t>
+          <t>4842; 18754</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>53090; 71185</t>
+          <t>56716; 76621</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2216; 12438</t>
+          <t>2119; 11391</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>35040; 59908</t>
+          <t>34630; 58578</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7695; 23127</t>
+          <t>7477; 22455</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>69861; 92198</t>
+          <t>74186; 98489</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22173</t>
+          <t>23480</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>68974</t>
+          <t>75295</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>91148</t>
+          <t>98775</t>
         </is>
       </c>
     </row>
@@ -1784,57 +1784,57 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4292; 16169</t>
+          <t>3809; 15906</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1616; 9403</t>
+          <t>1575; 9401</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15949; 29888</t>
+          <t>16799; 31442</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2188; 12254</t>
+          <t>2251; 12977</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29141; 53902</t>
+          <t>29788; 52982</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5291; 20263</t>
+          <t>5260; 20992</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>59452; 79282</t>
+          <t>66317; 86929</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2331; 14510</t>
+          <t>2297; 13806</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>37622; 61995</t>
+          <t>37746; 65453</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8984; 25963</t>
+          <t>8941; 25086</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>79688; 104508</t>
+          <t>86824; 112260</t>
         </is>
       </c>
     </row>
